--- a/excel_routes/route_DMM_CAI_threats.xlsx
+++ b/excel_routes/route_DMM_CAI_threats.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CODERED\LAB\Artifacts\outputs\run_generated_260726_at_14.46\reports\excel_routes\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CODERED\LAB\Artifacts\outputs\run_generated_270726_at_12.25\reports\excel_routes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F86E4414-8F22-4D30-9088-B09D28A83CCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D20F25C-E09F-41EF-B326-6F486F53D232}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="12972" yWindow="348" windowWidth="10068" windowHeight="10284" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="846" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="646" uniqueCount="81">
   <si>
     <t>Date</t>
   </si>
@@ -63,61 +63,61 @@
     <t>27-JUL-26</t>
   </si>
   <si>
+    <t>SM-434</t>
+  </si>
+  <si>
+    <t>Nesma Airlines NE-151</t>
+  </si>
+  <si>
+    <t>MED</t>
+  </si>
+  <si>
+    <t>SAR</t>
+  </si>
+  <si>
+    <t>Nile Air NP-332</t>
+  </si>
+  <si>
+    <t>28-JUL-26</t>
+  </si>
+  <si>
+    <t>Nile Air NP-132</t>
+  </si>
+  <si>
+    <t>29-JUL-26</t>
+  </si>
+  <si>
+    <t>LOW</t>
+  </si>
+  <si>
+    <t>Nile Air NP-232</t>
+  </si>
+  <si>
+    <t>31-JUL-26</t>
+  </si>
+  <si>
     <t>SM-440</t>
   </si>
   <si>
-    <t>Nile Air NP-332</t>
-  </si>
-  <si>
-    <t>MED</t>
-  </si>
-  <si>
-    <t>SAR</t>
+    <t>02-AUG-26</t>
+  </si>
+  <si>
+    <t>Nesma Airlines NE-153</t>
+  </si>
+  <si>
+    <t>Nile Air NP-234</t>
+  </si>
+  <si>
+    <t>flynas XY-894</t>
+  </si>
+  <si>
+    <t>03-AUG-26</t>
   </si>
   <si>
     <t>Nile Air NP-334</t>
   </si>
   <si>
-    <t>Nesma Airlines NE-151</t>
-  </si>
-  <si>
-    <t>EgyptAir MS-688</t>
-  </si>
-  <si>
-    <t>LOW</t>
-  </si>
-  <si>
-    <t>28-JUL-26</t>
-  </si>
-  <si>
-    <t>SM-434</t>
-  </si>
-  <si>
-    <t>Nile Air NP-132</t>
-  </si>
-  <si>
-    <t>29-JUL-26</t>
-  </si>
-  <si>
-    <t>Nile Air NP-232</t>
-  </si>
-  <si>
-    <t>31-JUL-26</t>
-  </si>
-  <si>
-    <t>02-AUG-26</t>
-  </si>
-  <si>
-    <t>Nesma Airlines NE-153</t>
-  </si>
-  <si>
-    <t>Nile Air NP-234</t>
-  </si>
-  <si>
-    <t>03-AUG-26</t>
-  </si>
-  <si>
-    <t>flynas XY-894</t>
+    <t>EgyptAir MS-682</t>
   </si>
   <si>
     <t>04-AUG-26</t>
@@ -138,9 +138,6 @@
     <t>Air Arabia Egypt E5-316</t>
   </si>
   <si>
-    <t>EgyptAir MS-682</t>
-  </si>
-  <si>
     <t>09-AUG-26</t>
   </si>
   <si>
@@ -198,18 +195,6 @@
     <t>01-SEP-26</t>
   </si>
   <si>
-    <t>flyadeal F3-911</t>
-  </si>
-  <si>
-    <t>02-SEP-26</t>
-  </si>
-  <si>
-    <t>04-SEP-26</t>
-  </si>
-  <si>
-    <t>06-SEP-26</t>
-  </si>
-  <si>
     <t>08-SEP-26</t>
   </si>
   <si>
@@ -222,12 +207,6 @@
     <t>15-SEP-26</t>
   </si>
   <si>
-    <t>16-SEP-26</t>
-  </si>
-  <si>
-    <t>18-SEP-26</t>
-  </si>
-  <si>
     <t>20-SEP-26</t>
   </si>
   <si>
@@ -240,88 +219,55 @@
     <t>27-SEP-26</t>
   </si>
   <si>
-    <t>28-SEP-26</t>
-  </si>
-  <si>
     <t>29-SEP-26</t>
   </si>
   <si>
     <t>02-OCT-26</t>
   </si>
   <si>
-    <t>04-OCT-26</t>
-  </si>
-  <si>
-    <t>16-OCT-26</t>
+    <t>06-OCT-26</t>
+  </si>
+  <si>
+    <t>19-OCT-26</t>
+  </si>
+  <si>
+    <t>21-OCT-26</t>
   </si>
   <si>
     <t>25-OCT-26</t>
   </si>
   <si>
+    <t>27-OCT-26</t>
+  </si>
+  <si>
+    <t>flynas XY-854</t>
+  </si>
+  <si>
+    <t>30-OCT-26</t>
+  </si>
+  <si>
     <t>31-OCT-26</t>
   </si>
   <si>
-    <t>flynas XY-854</t>
-  </si>
-  <si>
-    <t>19-NOV-26</t>
-  </si>
-  <si>
     <t>20-NOV-26</t>
   </si>
   <si>
     <t>21-NOV-26</t>
   </si>
   <si>
-    <t>26-NOV-26</t>
-  </si>
-  <si>
-    <t>27-NOV-26</t>
-  </si>
-  <si>
     <t>28-NOV-26</t>
   </si>
   <si>
-    <t>01-DEC-26</t>
-  </si>
-  <si>
-    <t>03-DEC-26</t>
-  </si>
-  <si>
-    <t>04-DEC-26</t>
-  </si>
-  <si>
     <t>05-DEC-26</t>
   </si>
   <si>
-    <t>08-DEC-26</t>
-  </si>
-  <si>
-    <t>11-DEC-26</t>
-  </si>
-  <si>
     <t>12-DEC-26</t>
   </si>
   <si>
-    <t>15-DEC-26</t>
-  </si>
-  <si>
-    <t>17-DEC-26</t>
-  </si>
-  <si>
     <t>19-DEC-26</t>
   </si>
   <si>
-    <t>22-DEC-26</t>
-  </si>
-  <si>
-    <t>24-DEC-26</t>
-  </si>
-  <si>
     <t>26-DEC-26</t>
-  </si>
-  <si>
-    <t>29-DEC-26</t>
   </si>
 </sst>
 </file>
@@ -718,7 +664,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:K168"/>
+  <dimension ref="A1:K128"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -779,13 +725,13 @@
         <v>13</v>
       </c>
       <c r="D2" s="2">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E2" s="2">
         <v>415</v>
       </c>
       <c r="F2" s="2">
-        <v>-62</v>
+        <v>-64</v>
       </c>
       <c r="G2" s="2">
         <v>40</v>
@@ -840,22 +786,22 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D4" s="2">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="E4" s="2">
         <v>415</v>
       </c>
       <c r="F4" s="2">
-        <v>-56</v>
+        <v>-64</v>
       </c>
       <c r="G4" s="2">
         <v>40</v>
@@ -875,7 +821,7 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>12</v>
@@ -884,25 +830,25 @@
         <v>18</v>
       </c>
       <c r="D5" s="2">
-        <v>472</v>
+        <v>353</v>
       </c>
       <c r="E5" s="2">
         <v>415</v>
       </c>
       <c r="F5" s="2">
-        <v>57</v>
+        <v>-62</v>
       </c>
       <c r="G5" s="2">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H5" s="2">
         <v>30</v>
       </c>
       <c r="I5" s="2">
-        <v>-16</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>19</v>
+        <v>-10</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>15</v>
@@ -910,22 +856,22 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D6" s="2">
-        <v>359</v>
+        <v>420</v>
       </c>
       <c r="E6" s="2">
         <v>415</v>
       </c>
       <c r="F6" s="2">
-        <v>-56</v>
+        <v>5</v>
       </c>
       <c r="G6" s="2">
         <v>40</v>
@@ -936,8 +882,8 @@
       <c r="I6" s="2">
         <v>-10</v>
       </c>
-      <c r="J6" s="3" t="s">
-        <v>14</v>
+      <c r="J6" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>15</v>
@@ -945,13 +891,13 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>21</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>22</v>
       </c>
       <c r="D7" s="2">
         <v>421</v>
@@ -972,7 +918,7 @@
         <v>-10</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>15</v>
@@ -980,22 +926,22 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>21</v>
-      </c>
       <c r="C8" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D8" s="2">
-        <v>359</v>
+        <v>420</v>
       </c>
       <c r="E8" s="2">
-        <v>415</v>
+        <v>521</v>
       </c>
       <c r="F8" s="2">
-        <v>-56</v>
+        <v>-101</v>
       </c>
       <c r="G8" s="2">
         <v>40</v>
@@ -1015,22 +961,22 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="C9" s="2" t="s">
         <v>21</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="D9" s="2">
         <v>421</v>
       </c>
       <c r="E9" s="2">
-        <v>415</v>
+        <v>521</v>
       </c>
       <c r="F9" s="2">
-        <v>6</v>
+        <v>-100</v>
       </c>
       <c r="G9" s="2">
         <v>40</v>
@@ -1041,8 +987,8 @@
       <c r="I9" s="2">
         <v>-10</v>
       </c>
-      <c r="J9" s="4" t="s">
-        <v>19</v>
+      <c r="J9" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>15</v>
@@ -1050,22 +996,22 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>17</v>
-      </c>
       <c r="D10" s="2">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="E10" s="2">
-        <v>556</v>
+        <v>415</v>
       </c>
       <c r="F10" s="2">
-        <v>-197</v>
+        <v>-64</v>
       </c>
       <c r="G10" s="2">
         <v>40</v>
@@ -1085,22 +1031,22 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="D11" s="2">
-        <v>421</v>
+        <v>351</v>
       </c>
       <c r="E11" s="2">
-        <v>556</v>
+        <v>415</v>
       </c>
       <c r="F11" s="2">
-        <v>-135</v>
+        <v>-64</v>
       </c>
       <c r="G11" s="2">
         <v>40</v>
@@ -1120,22 +1066,22 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>27</v>
-      </c>
       <c r="D12" s="2">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="E12" s="2">
         <v>415</v>
       </c>
       <c r="F12" s="2">
-        <v>-56</v>
+        <v>-62</v>
       </c>
       <c r="G12" s="2">
         <v>40</v>
@@ -1155,22 +1101,22 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>17</v>
-      </c>
       <c r="D13" s="2">
-        <v>359</v>
+        <v>421</v>
       </c>
       <c r="E13" s="2">
         <v>415</v>
       </c>
       <c r="F13" s="2">
-        <v>-56</v>
+        <v>6</v>
       </c>
       <c r="G13" s="2">
         <v>40</v>
@@ -1181,8 +1127,8 @@
       <c r="I13" s="2">
         <v>-10</v>
       </c>
-      <c r="J13" s="3" t="s">
-        <v>14</v>
+      <c r="J13" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="K13" s="2" t="s">
         <v>15</v>
@@ -1190,22 +1136,22 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D14" s="2">
-        <v>421</v>
+        <v>564</v>
       </c>
       <c r="E14" s="2">
         <v>415</v>
       </c>
       <c r="F14" s="2">
-        <v>6</v>
+        <v>149</v>
       </c>
       <c r="G14" s="2">
         <v>40</v>
@@ -1217,7 +1163,7 @@
         <v>-10</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>15</v>
@@ -1225,22 +1171,22 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="D15" s="2">
-        <v>421</v>
+        <v>351</v>
       </c>
       <c r="E15" s="2">
-        <v>415</v>
+        <v>521</v>
       </c>
       <c r="F15" s="2">
-        <v>6</v>
+        <v>-170</v>
       </c>
       <c r="G15" s="2">
         <v>40</v>
@@ -1251,8 +1197,8 @@
       <c r="I15" s="2">
         <v>-10</v>
       </c>
-      <c r="J15" s="4" t="s">
-        <v>19</v>
+      <c r="J15" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K15" s="2" t="s">
         <v>15</v>
@@ -1260,22 +1206,22 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D16" s="2">
-        <v>359</v>
+        <v>421</v>
       </c>
       <c r="E16" s="2">
         <v>521</v>
       </c>
       <c r="F16" s="2">
-        <v>-162</v>
+        <v>-100</v>
       </c>
       <c r="G16" s="2">
         <v>40</v>
@@ -1295,13 +1241,13 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>13</v>
       </c>
       <c r="D17" s="2">
         <v>421</v>
@@ -1330,34 +1276,34 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="D18" s="2">
-        <v>421</v>
+        <v>705</v>
       </c>
       <c r="E18" s="2">
         <v>521</v>
       </c>
       <c r="F18" s="2">
-        <v>-100</v>
+        <v>184</v>
       </c>
       <c r="G18" s="2">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H18" s="2">
         <v>30</v>
       </c>
       <c r="I18" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>14</v>
+        <v>-16</v>
+      </c>
+      <c r="J18" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>15</v>
@@ -1365,22 +1311,22 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="D19" s="2">
-        <v>614</v>
+        <v>351</v>
       </c>
       <c r="E19" s="2">
         <v>521</v>
       </c>
       <c r="F19" s="2">
-        <v>93</v>
+        <v>-170</v>
       </c>
       <c r="G19" s="2">
         <v>40</v>
@@ -1391,8 +1337,8 @@
       <c r="I19" s="2">
         <v>-10</v>
       </c>
-      <c r="J19" s="4" t="s">
-        <v>19</v>
+      <c r="J19" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K19" s="2" t="s">
         <v>15</v>
@@ -1403,19 +1349,19 @@
         <v>31</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="D20" s="2">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="E20" s="2">
         <v>521</v>
       </c>
       <c r="F20" s="2">
-        <v>-162</v>
+        <v>-168</v>
       </c>
       <c r="G20" s="2">
         <v>40</v>
@@ -1438,19 +1384,19 @@
         <v>31</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="D21" s="2">
-        <v>421</v>
+        <v>353</v>
       </c>
       <c r="E21" s="2">
         <v>521</v>
       </c>
       <c r="F21" s="2">
-        <v>-100</v>
+        <v>-168</v>
       </c>
       <c r="G21" s="2">
         <v>40</v>
@@ -1470,22 +1416,22 @@
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="D22" s="2">
-        <v>421</v>
+        <v>351</v>
       </c>
       <c r="E22" s="2">
         <v>521</v>
       </c>
       <c r="F22" s="2">
-        <v>-100</v>
+        <v>-170</v>
       </c>
       <c r="G22" s="2">
         <v>40</v>
@@ -1505,22 +1451,22 @@
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D23" s="2">
-        <v>614</v>
+        <v>353</v>
       </c>
       <c r="E23" s="2">
         <v>521</v>
       </c>
       <c r="F23" s="2">
-        <v>93</v>
+        <v>-168</v>
       </c>
       <c r="G23" s="2">
         <v>40</v>
@@ -1531,8 +1477,8 @@
       <c r="I23" s="2">
         <v>-10</v>
       </c>
-      <c r="J23" s="4" t="s">
-        <v>19</v>
+      <c r="J23" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K23" s="2" t="s">
         <v>15</v>
@@ -1543,19 +1489,19 @@
         <v>33</v>
       </c>
       <c r="B24" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C24" s="2" t="s">
-        <v>17</v>
-      </c>
       <c r="D24" s="2">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="E24" s="2">
         <v>521</v>
       </c>
       <c r="F24" s="2">
-        <v>-162</v>
+        <v>-168</v>
       </c>
       <c r="G24" s="2">
         <v>40</v>
@@ -1578,10 +1524,10 @@
         <v>33</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D25" s="2">
         <v>421</v>
@@ -1610,22 +1556,22 @@
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D26" s="2">
-        <v>421</v>
+        <v>351</v>
       </c>
       <c r="E26" s="2">
         <v>521</v>
       </c>
       <c r="F26" s="2">
-        <v>-100</v>
+        <v>-170</v>
       </c>
       <c r="G26" s="2">
         <v>40</v>
@@ -1645,22 +1591,22 @@
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="D27" s="2">
-        <v>421</v>
+        <v>351</v>
       </c>
       <c r="E27" s="2">
         <v>521</v>
       </c>
       <c r="F27" s="2">
-        <v>-100</v>
+        <v>-170</v>
       </c>
       <c r="G27" s="2">
         <v>40</v>
@@ -1680,22 +1626,22 @@
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D28" s="2">
-        <v>644</v>
+        <v>353</v>
       </c>
       <c r="E28" s="2">
         <v>521</v>
       </c>
       <c r="F28" s="2">
-        <v>123</v>
+        <v>-168</v>
       </c>
       <c r="G28" s="2">
         <v>40</v>
@@ -1706,8 +1652,8 @@
       <c r="I28" s="2">
         <v>-10</v>
       </c>
-      <c r="J28" s="4" t="s">
-        <v>19</v>
+      <c r="J28" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K28" s="2" t="s">
         <v>15</v>
@@ -1718,19 +1664,19 @@
         <v>35</v>
       </c>
       <c r="B29" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C29" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C29" s="2" t="s">
-        <v>27</v>
-      </c>
       <c r="D29" s="2">
-        <v>359</v>
+        <v>421</v>
       </c>
       <c r="E29" s="2">
         <v>521</v>
       </c>
       <c r="F29" s="2">
-        <v>-162</v>
+        <v>-100</v>
       </c>
       <c r="G29" s="2">
         <v>40</v>
@@ -1753,19 +1699,19 @@
         <v>35</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D30" s="2">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="E30" s="2">
-        <v>521</v>
+        <v>556</v>
       </c>
       <c r="F30" s="2">
-        <v>-162</v>
+        <v>-205</v>
       </c>
       <c r="G30" s="2">
         <v>40</v>
@@ -1788,19 +1734,19 @@
         <v>35</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="D31" s="2">
-        <v>421</v>
+        <v>351</v>
       </c>
       <c r="E31" s="2">
-        <v>521</v>
+        <v>556</v>
       </c>
       <c r="F31" s="2">
-        <v>-100</v>
+        <v>-205</v>
       </c>
       <c r="G31" s="2">
         <v>40</v>
@@ -1823,19 +1769,19 @@
         <v>35</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D32" s="2">
-        <v>421</v>
+        <v>353</v>
       </c>
       <c r="E32" s="2">
-        <v>521</v>
+        <v>556</v>
       </c>
       <c r="F32" s="2">
-        <v>-100</v>
+        <v>-203</v>
       </c>
       <c r="G32" s="2">
         <v>40</v>
@@ -1858,31 +1804,31 @@
         <v>35</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="D33" s="2">
-        <v>614</v>
+        <v>398</v>
       </c>
       <c r="E33" s="2">
-        <v>521</v>
+        <v>556</v>
       </c>
       <c r="F33" s="2">
-        <v>93</v>
+        <v>-158</v>
       </c>
       <c r="G33" s="2">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="H33" s="2">
         <v>30</v>
       </c>
       <c r="I33" s="2">
-        <v>-10</v>
+        <v>10</v>
       </c>
       <c r="J33" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K33" s="2" t="s">
         <v>15</v>
@@ -1893,19 +1839,19 @@
         <v>35</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D34" s="2">
-        <v>359</v>
+        <v>421</v>
       </c>
       <c r="E34" s="2">
         <v>556</v>
       </c>
       <c r="F34" s="2">
-        <v>-197</v>
+        <v>-135</v>
       </c>
       <c r="G34" s="2">
         <v>40</v>
@@ -1928,31 +1874,31 @@
         <v>35</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="D35" s="2">
-        <v>359</v>
+        <v>773</v>
       </c>
       <c r="E35" s="2">
         <v>556</v>
       </c>
       <c r="F35" s="2">
-        <v>-197</v>
+        <v>217</v>
       </c>
       <c r="G35" s="2">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H35" s="2">
         <v>30</v>
       </c>
       <c r="I35" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J35" s="3" t="s">
-        <v>14</v>
+        <v>-16</v>
+      </c>
+      <c r="J35" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="K35" s="2" t="s">
         <v>15</v>
@@ -1960,34 +1906,34 @@
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="D36" s="2">
-        <v>400</v>
+        <v>351</v>
       </c>
       <c r="E36" s="2">
-        <v>556</v>
+        <v>415</v>
       </c>
       <c r="F36" s="2">
-        <v>-156</v>
+        <v>-64</v>
       </c>
       <c r="G36" s="2">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="H36" s="2">
         <v>30</v>
       </c>
       <c r="I36" s="2">
-        <v>10</v>
-      </c>
-      <c r="J36" s="4" t="s">
-        <v>19</v>
+        <v>-10</v>
+      </c>
+      <c r="J36" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K36" s="2" t="s">
         <v>15</v>
@@ -1995,22 +1941,22 @@
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="D37" s="2">
-        <v>421</v>
+        <v>351</v>
       </c>
       <c r="E37" s="2">
-        <v>556</v>
+        <v>415</v>
       </c>
       <c r="F37" s="2">
-        <v>-135</v>
+        <v>-64</v>
       </c>
       <c r="G37" s="2">
         <v>40</v>
@@ -2030,22 +1976,22 @@
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D38" s="2">
-        <v>421</v>
+        <v>353</v>
       </c>
       <c r="E38" s="2">
-        <v>556</v>
+        <v>415</v>
       </c>
       <c r="F38" s="2">
-        <v>-135</v>
+        <v>-62</v>
       </c>
       <c r="G38" s="2">
         <v>40</v>
@@ -2065,22 +2011,22 @@
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="D39" s="2">
-        <v>614</v>
+        <v>353</v>
       </c>
       <c r="E39" s="2">
-        <v>556</v>
+        <v>415</v>
       </c>
       <c r="F39" s="2">
-        <v>58</v>
+        <v>-62</v>
       </c>
       <c r="G39" s="2">
         <v>40</v>
@@ -2091,8 +2037,8 @@
       <c r="I39" s="2">
         <v>-10</v>
       </c>
-      <c r="J39" s="4" t="s">
-        <v>19</v>
+      <c r="J39" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K39" s="2" t="s">
         <v>15</v>
@@ -2100,34 +2046,34 @@
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="D40" s="2">
-        <v>773</v>
+        <v>421</v>
       </c>
       <c r="E40" s="2">
-        <v>556</v>
+        <v>415</v>
       </c>
       <c r="F40" s="2">
-        <v>217</v>
+        <v>6</v>
       </c>
       <c r="G40" s="2">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H40" s="2">
         <v>30</v>
       </c>
       <c r="I40" s="2">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J40" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K40" s="2" t="s">
         <v>15</v>
@@ -2135,22 +2081,22 @@
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="D41" s="2">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E41" s="2">
         <v>415</v>
       </c>
       <c r="F41" s="2">
-        <v>-62</v>
+        <v>-64</v>
       </c>
       <c r="G41" s="2">
         <v>40</v>
@@ -2170,13 +2116,13 @@
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D42" s="2">
         <v>353</v>
@@ -2205,22 +2151,22 @@
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D43" s="2">
-        <v>359</v>
+        <v>421</v>
       </c>
       <c r="E43" s="2">
         <v>415</v>
       </c>
       <c r="F43" s="2">
-        <v>-56</v>
+        <v>6</v>
       </c>
       <c r="G43" s="2">
         <v>40</v>
@@ -2231,8 +2177,8 @@
       <c r="I43" s="2">
         <v>-10</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>14</v>
+      <c r="J43" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="K43" s="2" t="s">
         <v>15</v>
@@ -2240,22 +2186,22 @@
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D44" s="2">
-        <v>359</v>
+        <v>421</v>
       </c>
       <c r="E44" s="2">
         <v>415</v>
       </c>
       <c r="F44" s="2">
-        <v>-56</v>
+        <v>6</v>
       </c>
       <c r="G44" s="2">
         <v>40</v>
@@ -2266,8 +2212,8 @@
       <c r="I44" s="2">
         <v>-10</v>
       </c>
-      <c r="J44" s="3" t="s">
-        <v>14</v>
+      <c r="J44" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="K44" s="2" t="s">
         <v>15</v>
@@ -2275,22 +2221,22 @@
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="D45" s="2">
-        <v>421</v>
+        <v>351</v>
       </c>
       <c r="E45" s="2">
         <v>415</v>
       </c>
       <c r="F45" s="2">
-        <v>6</v>
+        <v>-64</v>
       </c>
       <c r="G45" s="2">
         <v>40</v>
@@ -2301,8 +2247,8 @@
       <c r="I45" s="2">
         <v>-10</v>
       </c>
-      <c r="J45" s="4" t="s">
-        <v>19</v>
+      <c r="J45" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K45" s="2" t="s">
         <v>15</v>
@@ -2313,19 +2259,19 @@
         <v>40</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="D46" s="2">
-        <v>353</v>
+        <v>421</v>
       </c>
       <c r="E46" s="2">
         <v>415</v>
       </c>
       <c r="F46" s="2">
-        <v>-62</v>
+        <v>6</v>
       </c>
       <c r="G46" s="2">
         <v>40</v>
@@ -2336,8 +2282,8 @@
       <c r="I46" s="2">
         <v>-10</v>
       </c>
-      <c r="J46" s="3" t="s">
-        <v>14</v>
+      <c r="J46" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="K46" s="2" t="s">
         <v>15</v>
@@ -2348,19 +2294,19 @@
         <v>40</v>
       </c>
       <c r="B47" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C47" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C47" s="2" t="s">
-        <v>17</v>
-      </c>
       <c r="D47" s="2">
-        <v>359</v>
+        <v>421</v>
       </c>
       <c r="E47" s="2">
         <v>415</v>
       </c>
       <c r="F47" s="2">
-        <v>-56</v>
+        <v>6</v>
       </c>
       <c r="G47" s="2">
         <v>40</v>
@@ -2371,8 +2317,8 @@
       <c r="I47" s="2">
         <v>-10</v>
       </c>
-      <c r="J47" s="3" t="s">
-        <v>14</v>
+      <c r="J47" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="K47" s="2" t="s">
         <v>15</v>
@@ -2383,10 +2329,10 @@
         <v>40</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D48" s="2">
         <v>421</v>
@@ -2407,7 +2353,7 @@
         <v>-10</v>
       </c>
       <c r="J48" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K48" s="2" t="s">
         <v>15</v>
@@ -2415,13 +2361,13 @@
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D49" s="2">
         <v>421</v>
@@ -2442,7 +2388,7 @@
         <v>-10</v>
       </c>
       <c r="J49" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K49" s="2" t="s">
         <v>15</v>
@@ -2453,19 +2399,19 @@
         <v>41</v>
       </c>
       <c r="B50" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C50" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C50" s="2" t="s">
-        <v>27</v>
-      </c>
       <c r="D50" s="2">
-        <v>359</v>
+        <v>421</v>
       </c>
       <c r="E50" s="2">
         <v>415</v>
       </c>
       <c r="F50" s="2">
-        <v>-56</v>
+        <v>6</v>
       </c>
       <c r="G50" s="2">
         <v>40</v>
@@ -2476,8 +2422,8 @@
       <c r="I50" s="2">
         <v>-10</v>
       </c>
-      <c r="J50" s="3" t="s">
-        <v>14</v>
+      <c r="J50" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="K50" s="2" t="s">
         <v>15</v>
@@ -2485,22 +2431,22 @@
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="D51" s="2">
-        <v>421</v>
+        <v>351</v>
       </c>
       <c r="E51" s="2">
         <v>415</v>
       </c>
       <c r="F51" s="2">
-        <v>6</v>
+        <v>-64</v>
       </c>
       <c r="G51" s="2">
         <v>40</v>
@@ -2511,8 +2457,8 @@
       <c r="I51" s="2">
         <v>-10</v>
       </c>
-      <c r="J51" s="4" t="s">
-        <v>19</v>
+      <c r="J51" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K51" s="2" t="s">
         <v>15</v>
@@ -2520,22 +2466,22 @@
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D52" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E52" s="2">
         <v>415</v>
       </c>
       <c r="F52" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G52" s="2">
         <v>40</v>
@@ -2547,7 +2493,7 @@
         <v>-10</v>
       </c>
       <c r="J52" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K52" s="2" t="s">
         <v>15</v>
@@ -2555,13 +2501,13 @@
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="D53" s="2">
         <v>421</v>
@@ -2582,7 +2528,7 @@
         <v>-10</v>
       </c>
       <c r="J53" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K53" s="2" t="s">
         <v>15</v>
@@ -2596,7 +2542,7 @@
         <v>12</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D54" s="2">
         <v>421</v>
@@ -2617,7 +2563,7 @@
         <v>-10</v>
       </c>
       <c r="J54" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K54" s="2" t="s">
         <v>15</v>
@@ -2625,22 +2571,22 @@
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D55" s="2">
-        <v>421</v>
+        <v>351</v>
       </c>
       <c r="E55" s="2">
         <v>415</v>
       </c>
       <c r="F55" s="2">
-        <v>6</v>
+        <v>-64</v>
       </c>
       <c r="G55" s="2">
         <v>40</v>
@@ -2651,8 +2597,8 @@
       <c r="I55" s="2">
         <v>-10</v>
       </c>
-      <c r="J55" s="4" t="s">
-        <v>19</v>
+      <c r="J55" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K55" s="2" t="s">
         <v>15</v>
@@ -2663,19 +2609,19 @@
         <v>43</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D56" s="2">
-        <v>359</v>
+        <v>421</v>
       </c>
       <c r="E56" s="2">
         <v>415</v>
       </c>
       <c r="F56" s="2">
-        <v>-56</v>
+        <v>6</v>
       </c>
       <c r="G56" s="2">
         <v>40</v>
@@ -2686,8 +2632,8 @@
       <c r="I56" s="2">
         <v>-10</v>
       </c>
-      <c r="J56" s="3" t="s">
-        <v>14</v>
+      <c r="J56" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="K56" s="2" t="s">
         <v>15</v>
@@ -2695,22 +2641,22 @@
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="D57" s="2">
-        <v>420</v>
+        <v>351</v>
       </c>
       <c r="E57" s="2">
         <v>415</v>
       </c>
       <c r="F57" s="2">
-        <v>5</v>
+        <v>-64</v>
       </c>
       <c r="G57" s="2">
         <v>40</v>
@@ -2721,8 +2667,8 @@
       <c r="I57" s="2">
         <v>-10</v>
       </c>
-      <c r="J57" s="4" t="s">
-        <v>19</v>
+      <c r="J57" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K57" s="2" t="s">
         <v>15</v>
@@ -2730,22 +2676,22 @@
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D58" s="2">
-        <v>421</v>
+        <v>353</v>
       </c>
       <c r="E58" s="2">
         <v>415</v>
       </c>
       <c r="F58" s="2">
-        <v>6</v>
+        <v>-62</v>
       </c>
       <c r="G58" s="2">
         <v>40</v>
@@ -2756,8 +2702,8 @@
       <c r="I58" s="2">
         <v>-10</v>
       </c>
-      <c r="J58" s="4" t="s">
-        <v>19</v>
+      <c r="J58" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K58" s="2" t="s">
         <v>15</v>
@@ -2765,13 +2711,13 @@
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="D59" s="2">
         <v>421</v>
@@ -2792,7 +2738,7 @@
         <v>-10</v>
       </c>
       <c r="J59" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K59" s="2" t="s">
         <v>15</v>
@@ -2809,13 +2755,13 @@
         <v>27</v>
       </c>
       <c r="D60" s="2">
-        <v>359</v>
+        <v>564</v>
       </c>
       <c r="E60" s="2">
         <v>415</v>
       </c>
       <c r="F60" s="2">
-        <v>-56</v>
+        <v>149</v>
       </c>
       <c r="G60" s="2">
         <v>40</v>
@@ -2826,8 +2772,8 @@
       <c r="I60" s="2">
         <v>-10</v>
       </c>
-      <c r="J60" s="3" t="s">
-        <v>14</v>
+      <c r="J60" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="K60" s="2" t="s">
         <v>15</v>
@@ -2835,22 +2781,22 @@
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="D61" s="2">
-        <v>421</v>
+        <v>351</v>
       </c>
       <c r="E61" s="2">
         <v>415</v>
       </c>
       <c r="F61" s="2">
-        <v>6</v>
+        <v>-64</v>
       </c>
       <c r="G61" s="2">
         <v>40</v>
@@ -2861,8 +2807,8 @@
       <c r="I61" s="2">
         <v>-10</v>
       </c>
-      <c r="J61" s="4" t="s">
-        <v>19</v>
+      <c r="J61" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K61" s="2" t="s">
         <v>15</v>
@@ -2873,10 +2819,10 @@
         <v>45</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D62" s="2">
         <v>353</v>
@@ -2908,19 +2854,19 @@
         <v>45</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="D63" s="2">
-        <v>359</v>
+        <v>421</v>
       </c>
       <c r="E63" s="2">
         <v>415</v>
       </c>
       <c r="F63" s="2">
-        <v>-56</v>
+        <v>6</v>
       </c>
       <c r="G63" s="2">
         <v>40</v>
@@ -2931,8 +2877,8 @@
       <c r="I63" s="2">
         <v>-10</v>
       </c>
-      <c r="J63" s="3" t="s">
-        <v>14</v>
+      <c r="J63" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="K63" s="2" t="s">
         <v>15</v>
@@ -2943,10 +2889,10 @@
         <v>45</v>
       </c>
       <c r="B64" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C64" s="2" t="s">
         <v>21</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>22</v>
       </c>
       <c r="D64" s="2">
         <v>421</v>
@@ -2967,7 +2913,7 @@
         <v>-10</v>
       </c>
       <c r="J64" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K64" s="2" t="s">
         <v>15</v>
@@ -2978,19 +2924,19 @@
         <v>46</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="D65" s="2">
-        <v>353</v>
+        <v>421</v>
       </c>
       <c r="E65" s="2">
-        <v>415</v>
+        <v>521</v>
       </c>
       <c r="F65" s="2">
-        <v>-62</v>
+        <v>-100</v>
       </c>
       <c r="G65" s="2">
         <v>40</v>
@@ -3013,19 +2959,19 @@
         <v>46</v>
       </c>
       <c r="B66" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C66" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C66" s="2" t="s">
-        <v>27</v>
-      </c>
       <c r="D66" s="2">
-        <v>359</v>
+        <v>421</v>
       </c>
       <c r="E66" s="2">
-        <v>415</v>
+        <v>521</v>
       </c>
       <c r="F66" s="2">
-        <v>-56</v>
+        <v>-100</v>
       </c>
       <c r="G66" s="2">
         <v>40</v>
@@ -3048,10 +2994,10 @@
         <v>46</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D67" s="2">
         <v>421</v>
@@ -3072,7 +3018,7 @@
         <v>-10</v>
       </c>
       <c r="J67" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K67" s="2" t="s">
         <v>15</v>
@@ -3083,10 +3029,10 @@
         <v>46</v>
       </c>
       <c r="B68" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C68" s="2" t="s">
         <v>21</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="D68" s="2">
         <v>421</v>
@@ -3107,7 +3053,7 @@
         <v>-10</v>
       </c>
       <c r="J68" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K68" s="2" t="s">
         <v>15</v>
@@ -3118,19 +3064,19 @@
         <v>47</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D69" s="2">
-        <v>421</v>
+        <v>351</v>
       </c>
       <c r="E69" s="2">
-        <v>521</v>
+        <v>415</v>
       </c>
       <c r="F69" s="2">
-        <v>-100</v>
+        <v>-64</v>
       </c>
       <c r="G69" s="2">
         <v>40</v>
@@ -3153,19 +3099,19 @@
         <v>47</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D70" s="2">
         <v>421</v>
       </c>
       <c r="E70" s="2">
-        <v>521</v>
+        <v>415</v>
       </c>
       <c r="F70" s="2">
-        <v>-100</v>
+        <v>6</v>
       </c>
       <c r="G70" s="2">
         <v>40</v>
@@ -3176,8 +3122,8 @@
       <c r="I70" s="2">
         <v>-10</v>
       </c>
-      <c r="J70" s="3" t="s">
-        <v>14</v>
+      <c r="J70" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="K70" s="2" t="s">
         <v>15</v>
@@ -3188,19 +3134,19 @@
         <v>47</v>
       </c>
       <c r="B71" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C71" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C71" s="2" t="s">
-        <v>30</v>
-      </c>
       <c r="D71" s="2">
-        <v>584</v>
+        <v>421</v>
       </c>
       <c r="E71" s="2">
-        <v>521</v>
+        <v>415</v>
       </c>
       <c r="F71" s="2">
-        <v>63</v>
+        <v>6</v>
       </c>
       <c r="G71" s="2">
         <v>40</v>
@@ -3212,7 +3158,7 @@
         <v>-10</v>
       </c>
       <c r="J71" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K71" s="2" t="s">
         <v>15</v>
@@ -3220,22 +3166,22 @@
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="D72" s="2">
-        <v>421</v>
+        <v>351</v>
       </c>
       <c r="E72" s="2">
         <v>415</v>
       </c>
       <c r="F72" s="2">
-        <v>6</v>
+        <v>-64</v>
       </c>
       <c r="G72" s="2">
         <v>40</v>
@@ -3246,8 +3192,8 @@
       <c r="I72" s="2">
         <v>-10</v>
       </c>
-      <c r="J72" s="4" t="s">
-        <v>19</v>
+      <c r="J72" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K72" s="2" t="s">
         <v>15</v>
@@ -3255,22 +3201,22 @@
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D73" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E73" s="2">
         <v>415</v>
       </c>
       <c r="F73" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G73" s="2">
         <v>40</v>
@@ -3282,7 +3228,7 @@
         <v>-10</v>
       </c>
       <c r="J73" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K73" s="2" t="s">
         <v>15</v>
@@ -3293,19 +3239,19 @@
         <v>48</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="D74" s="2">
-        <v>359</v>
+        <v>421</v>
       </c>
       <c r="E74" s="2">
         <v>415</v>
       </c>
       <c r="F74" s="2">
-        <v>-56</v>
+        <v>6</v>
       </c>
       <c r="G74" s="2">
         <v>40</v>
@@ -3316,8 +3262,8 @@
       <c r="I74" s="2">
         <v>-10</v>
       </c>
-      <c r="J74" s="3" t="s">
-        <v>14</v>
+      <c r="J74" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="K74" s="2" t="s">
         <v>15</v>
@@ -3325,22 +3271,22 @@
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="D75" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E75" s="2">
         <v>415</v>
       </c>
       <c r="F75" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G75" s="2">
         <v>40</v>
@@ -3352,7 +3298,7 @@
         <v>-10</v>
       </c>
       <c r="J75" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K75" s="2" t="s">
         <v>15</v>
@@ -3360,13 +3306,13 @@
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="D76" s="2">
         <v>421</v>
@@ -3387,7 +3333,7 @@
         <v>-10</v>
       </c>
       <c r="J76" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K76" s="2" t="s">
         <v>15</v>
@@ -3401,16 +3347,16 @@
         <v>12</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D77" s="2">
-        <v>359</v>
+        <v>421</v>
       </c>
       <c r="E77" s="2">
         <v>415</v>
       </c>
       <c r="F77" s="2">
-        <v>-56</v>
+        <v>6</v>
       </c>
       <c r="G77" s="2">
         <v>40</v>
@@ -3421,8 +3367,8 @@
       <c r="I77" s="2">
         <v>-10</v>
       </c>
-      <c r="J77" s="3" t="s">
-        <v>14</v>
+      <c r="J77" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="K77" s="2" t="s">
         <v>15</v>
@@ -3430,13 +3376,13 @@
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D78" s="2">
         <v>420</v>
@@ -3457,7 +3403,7 @@
         <v>-10</v>
       </c>
       <c r="J78" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K78" s="2" t="s">
         <v>15</v>
@@ -3465,7 +3411,7 @@
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>12</v>
@@ -3474,13 +3420,13 @@
         <v>13</v>
       </c>
       <c r="D79" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E79" s="2">
         <v>415</v>
       </c>
       <c r="F79" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G79" s="2">
         <v>40</v>
@@ -3492,7 +3438,7 @@
         <v>-10</v>
       </c>
       <c r="J79" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K79" s="2" t="s">
         <v>15</v>
@@ -3503,19 +3449,19 @@
         <v>50</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="D80" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E80" s="2">
         <v>415</v>
       </c>
       <c r="F80" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G80" s="2">
         <v>40</v>
@@ -3527,7 +3473,7 @@
         <v>-10</v>
       </c>
       <c r="J80" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K80" s="2" t="s">
         <v>15</v>
@@ -3538,19 +3484,19 @@
         <v>50</v>
       </c>
       <c r="B81" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C81" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C81" s="2" t="s">
-        <v>32</v>
-      </c>
       <c r="D81" s="2">
-        <v>421</v>
+        <v>544</v>
       </c>
       <c r="E81" s="2">
         <v>415</v>
       </c>
       <c r="F81" s="2">
-        <v>6</v>
+        <v>129</v>
       </c>
       <c r="G81" s="2">
         <v>40</v>
@@ -3562,7 +3508,7 @@
         <v>-10</v>
       </c>
       <c r="J81" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K81" s="2" t="s">
         <v>15</v>
@@ -3570,22 +3516,22 @@
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>22</v>
+        <v>52</v>
       </c>
       <c r="D82" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E82" s="2">
         <v>415</v>
       </c>
       <c r="F82" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G82" s="2">
         <v>40</v>
@@ -3597,7 +3543,7 @@
         <v>-10</v>
       </c>
       <c r="J82" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K82" s="2" t="s">
         <v>15</v>
@@ -3608,19 +3554,19 @@
         <v>51</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="D83" s="2">
-        <v>359</v>
+        <v>421</v>
       </c>
       <c r="E83" s="2">
         <v>415</v>
       </c>
       <c r="F83" s="2">
-        <v>-56</v>
+        <v>6</v>
       </c>
       <c r="G83" s="2">
         <v>40</v>
@@ -3631,8 +3577,8 @@
       <c r="I83" s="2">
         <v>-10</v>
       </c>
-      <c r="J83" s="3" t="s">
-        <v>14</v>
+      <c r="J83" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="K83" s="2" t="s">
         <v>15</v>
@@ -3643,19 +3589,19 @@
         <v>51</v>
       </c>
       <c r="B84" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C84" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C84" s="2" t="s">
-        <v>27</v>
-      </c>
       <c r="D84" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E84" s="2">
         <v>415</v>
       </c>
       <c r="F84" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G84" s="2">
         <v>40</v>
@@ -3667,7 +3613,7 @@
         <v>-10</v>
       </c>
       <c r="J84" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K84" s="2" t="s">
         <v>15</v>
@@ -3678,19 +3624,19 @@
         <v>51</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="D85" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E85" s="2">
-        <v>415</v>
+        <v>521</v>
       </c>
       <c r="F85" s="2">
-        <v>6</v>
+        <v>-101</v>
       </c>
       <c r="G85" s="2">
         <v>40</v>
@@ -3701,8 +3647,8 @@
       <c r="I85" s="2">
         <v>-10</v>
       </c>
-      <c r="J85" s="4" t="s">
-        <v>19</v>
+      <c r="J85" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K85" s="2" t="s">
         <v>15</v>
@@ -3713,19 +3659,19 @@
         <v>51</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D86" s="2">
-        <v>544</v>
+        <v>421</v>
       </c>
       <c r="E86" s="2">
-        <v>415</v>
+        <v>521</v>
       </c>
       <c r="F86" s="2">
-        <v>129</v>
+        <v>-100</v>
       </c>
       <c r="G86" s="2">
         <v>40</v>
@@ -3736,8 +3682,8 @@
       <c r="I86" s="2">
         <v>-10</v>
       </c>
-      <c r="J86" s="4" t="s">
-        <v>19</v>
+      <c r="J86" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K86" s="2" t="s">
         <v>15</v>
@@ -3745,22 +3691,22 @@
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B87" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C87" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C87" s="2" t="s">
-        <v>53</v>
-      </c>
       <c r="D87" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E87" s="2">
-        <v>415</v>
+        <v>521</v>
       </c>
       <c r="F87" s="2">
-        <v>5</v>
+        <v>-100</v>
       </c>
       <c r="G87" s="2">
         <v>40</v>
@@ -3771,8 +3717,8 @@
       <c r="I87" s="2">
         <v>-10</v>
       </c>
-      <c r="J87" s="4" t="s">
-        <v>19</v>
+      <c r="J87" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K87" s="2" t="s">
         <v>15</v>
@@ -3780,22 +3726,22 @@
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D88" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E88" s="2">
         <v>415</v>
       </c>
       <c r="F88" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G88" s="2">
         <v>40</v>
@@ -3807,7 +3753,7 @@
         <v>-10</v>
       </c>
       <c r="J88" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K88" s="2" t="s">
         <v>15</v>
@@ -3815,13 +3761,13 @@
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B89" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C89" s="2" t="s">
         <v>21</v>
-      </c>
-      <c r="C89" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="D89" s="2">
         <v>421</v>
@@ -3842,7 +3788,7 @@
         <v>-10</v>
       </c>
       <c r="J89" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K89" s="2" t="s">
         <v>15</v>
@@ -3850,22 +3796,22 @@
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A90" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="D90" s="2">
         <v>420</v>
       </c>
       <c r="E90" s="2">
-        <v>521</v>
+        <v>415</v>
       </c>
       <c r="F90" s="2">
-        <v>-101</v>
+        <v>5</v>
       </c>
       <c r="G90" s="2">
         <v>40</v>
@@ -3876,8 +3822,8 @@
       <c r="I90" s="2">
         <v>-10</v>
       </c>
-      <c r="J90" s="3" t="s">
-        <v>14</v>
+      <c r="J90" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="K90" s="2" t="s">
         <v>15</v>
@@ -3885,22 +3831,22 @@
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A91" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="D91" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E91" s="2">
-        <v>521</v>
+        <v>415</v>
       </c>
       <c r="F91" s="2">
-        <v>-100</v>
+        <v>5</v>
       </c>
       <c r="G91" s="2">
         <v>40</v>
@@ -3911,8 +3857,8 @@
       <c r="I91" s="2">
         <v>-10</v>
       </c>
-      <c r="J91" s="3" t="s">
-        <v>14</v>
+      <c r="J91" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="K91" s="2" t="s">
         <v>15</v>
@@ -3920,22 +3866,22 @@
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A92" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="D92" s="2">
         <v>421</v>
       </c>
       <c r="E92" s="2">
-        <v>521</v>
+        <v>415</v>
       </c>
       <c r="F92" s="2">
-        <v>-100</v>
+        <v>6</v>
       </c>
       <c r="G92" s="2">
         <v>40</v>
@@ -3946,8 +3892,8 @@
       <c r="I92" s="2">
         <v>-10</v>
       </c>
-      <c r="J92" s="3" t="s">
-        <v>14</v>
+      <c r="J92" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="K92" s="2" t="s">
         <v>15</v>
@@ -3955,22 +3901,22 @@
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A93" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D93" s="2">
-        <v>614</v>
+        <v>421</v>
       </c>
       <c r="E93" s="2">
-        <v>521</v>
+        <v>415</v>
       </c>
       <c r="F93" s="2">
-        <v>93</v>
+        <v>6</v>
       </c>
       <c r="G93" s="2">
         <v>40</v>
@@ -3982,7 +3928,7 @@
         <v>-10</v>
       </c>
       <c r="J93" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K93" s="2" t="s">
         <v>15</v>
@@ -3990,34 +3936,34 @@
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D94" s="2">
-        <v>420</v>
+        <v>369</v>
       </c>
       <c r="E94" s="2">
-        <v>415</v>
+        <v>623</v>
       </c>
       <c r="F94" s="2">
-        <v>5</v>
+        <v>-254</v>
       </c>
       <c r="G94" s="2">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="H94" s="2">
         <v>30</v>
       </c>
       <c r="I94" s="2">
-        <v>-10</v>
+        <v>15</v>
       </c>
       <c r="J94" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K94" s="2" t="s">
         <v>15</v>
@@ -4025,22 +3971,22 @@
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A95" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="D95" s="2">
-        <v>421</v>
+        <v>622</v>
       </c>
       <c r="E95" s="2">
-        <v>415</v>
+        <v>623</v>
       </c>
       <c r="F95" s="2">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="G95" s="2">
         <v>40</v>
@@ -4052,7 +3998,7 @@
         <v>-10</v>
       </c>
       <c r="J95" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K95" s="2" t="s">
         <v>15</v>
@@ -4060,22 +4006,22 @@
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A96" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B96" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="D96" s="2">
-        <v>420</v>
+        <v>540</v>
       </c>
       <c r="E96" s="2">
-        <v>415</v>
+        <v>578</v>
       </c>
       <c r="F96" s="2">
-        <v>5</v>
+        <v>-38</v>
       </c>
       <c r="G96" s="2">
         <v>40</v>
@@ -4087,7 +4033,7 @@
         <v>-10</v>
       </c>
       <c r="J96" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K96" s="2" t="s">
         <v>15</v>
@@ -4095,22 +4041,22 @@
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A97" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="D97" s="2">
-        <v>420</v>
+        <v>564</v>
       </c>
       <c r="E97" s="2">
-        <v>415</v>
+        <v>578</v>
       </c>
       <c r="F97" s="2">
-        <v>5</v>
+        <v>-14</v>
       </c>
       <c r="G97" s="2">
         <v>40</v>
@@ -4122,7 +4068,7 @@
         <v>-10</v>
       </c>
       <c r="J97" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K97" s="2" t="s">
         <v>15</v>
@@ -4130,22 +4076,22 @@
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="D98" s="2">
-        <v>421</v>
+        <v>564</v>
       </c>
       <c r="E98" s="2">
-        <v>415</v>
+        <v>539</v>
       </c>
       <c r="F98" s="2">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="G98" s="2">
         <v>40</v>
@@ -4157,7 +4103,7 @@
         <v>-10</v>
       </c>
       <c r="J98" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K98" s="2" t="s">
         <v>15</v>
@@ -4165,22 +4111,22 @@
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A99" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B99" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="D99" s="2">
+        <v>420</v>
+      </c>
+      <c r="E99" s="2">
         <v>421</v>
       </c>
-      <c r="E99" s="2">
-        <v>415</v>
-      </c>
       <c r="F99" s="2">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="G99" s="2">
         <v>40</v>
@@ -4192,7 +4138,7 @@
         <v>-10</v>
       </c>
       <c r="J99" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K99" s="2" t="s">
         <v>15</v>
@@ -4200,34 +4146,34 @@
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A100" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="D100" s="2">
-        <v>589</v>
+        <v>564</v>
       </c>
       <c r="E100" s="2">
-        <v>623</v>
+        <v>421</v>
       </c>
       <c r="F100" s="2">
-        <v>-34</v>
+        <v>143</v>
       </c>
       <c r="G100" s="2">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H100" s="2">
         <v>30</v>
       </c>
       <c r="I100" s="2">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="J100" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K100" s="2" t="s">
         <v>15</v>
@@ -4235,22 +4181,22 @@
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A101" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="D101" s="2">
-        <v>614</v>
+        <v>540</v>
       </c>
       <c r="E101" s="2">
-        <v>623</v>
+        <v>539</v>
       </c>
       <c r="F101" s="2">
-        <v>-9</v>
+        <v>1</v>
       </c>
       <c r="G101" s="2">
         <v>40</v>
@@ -4262,7 +4208,7 @@
         <v>-10</v>
       </c>
       <c r="J101" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K101" s="2" t="s">
         <v>15</v>
@@ -4270,22 +4216,22 @@
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A102" s="2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D102" s="2">
-        <v>630</v>
+        <v>622</v>
       </c>
       <c r="E102" s="2">
-        <v>623</v>
+        <v>578</v>
       </c>
       <c r="F102" s="2">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="G102" s="2">
         <v>40</v>
@@ -4297,7 +4243,7 @@
         <v>-10</v>
       </c>
       <c r="J102" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K102" s="2" t="s">
         <v>15</v>
@@ -4305,34 +4251,34 @@
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A103" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="D103" s="2">
-        <v>559</v>
+        <v>614</v>
       </c>
       <c r="E103" s="2">
-        <v>578</v>
+        <v>539</v>
       </c>
       <c r="F103" s="2">
-        <v>-19</v>
+        <v>75</v>
       </c>
       <c r="G103" s="2">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H103" s="2">
         <v>30</v>
       </c>
       <c r="I103" s="2">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="J103" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K103" s="2" t="s">
         <v>15</v>
@@ -4340,22 +4286,22 @@
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A104" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="D104" s="2">
-        <v>614</v>
+        <v>540</v>
       </c>
       <c r="E104" s="2">
-        <v>539</v>
+        <v>578</v>
       </c>
       <c r="F104" s="2">
-        <v>75</v>
+        <v>-38</v>
       </c>
       <c r="G104" s="2">
         <v>40</v>
@@ -4367,7 +4313,7 @@
         <v>-10</v>
       </c>
       <c r="J104" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K104" s="2" t="s">
         <v>15</v>
@@ -4375,22 +4321,22 @@
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A105" s="2" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B105" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D105" s="2">
-        <v>614</v>
+        <v>420</v>
       </c>
       <c r="E105" s="2">
-        <v>578</v>
+        <v>421</v>
       </c>
       <c r="F105" s="2">
-        <v>36</v>
+        <v>-1</v>
       </c>
       <c r="G105" s="2">
         <v>40</v>
@@ -4402,7 +4348,7 @@
         <v>-10</v>
       </c>
       <c r="J105" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K105" s="2" t="s">
         <v>15</v>
@@ -4410,22 +4356,22 @@
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A106" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="B106" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="D106" s="2">
-        <v>693</v>
+        <v>540</v>
       </c>
       <c r="E106" s="2">
-        <v>578</v>
+        <v>421</v>
       </c>
       <c r="F106" s="2">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G106" s="2">
         <v>40</v>
@@ -4437,7 +4383,7 @@
         <v>-10</v>
       </c>
       <c r="J106" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K106" s="2" t="s">
         <v>15</v>
@@ -4445,22 +4391,22 @@
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A107" s="2" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="D107" s="2">
-        <v>614</v>
+        <v>690</v>
       </c>
       <c r="E107" s="2">
-        <v>539</v>
+        <v>578</v>
       </c>
       <c r="F107" s="2">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="G107" s="2">
         <v>40</v>
@@ -4472,7 +4418,7 @@
         <v>-10</v>
       </c>
       <c r="J107" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K107" s="2" t="s">
         <v>15</v>
@@ -4480,22 +4426,22 @@
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A108" s="2" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="D108" s="2">
-        <v>550</v>
+        <v>564</v>
       </c>
       <c r="E108" s="2">
-        <v>578</v>
+        <v>421</v>
       </c>
       <c r="F108" s="2">
-        <v>-28</v>
+        <v>143</v>
       </c>
       <c r="G108" s="2">
         <v>40</v>
@@ -4507,7 +4453,7 @@
         <v>-10</v>
       </c>
       <c r="J108" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K108" s="2" t="s">
         <v>15</v>
@@ -4515,34 +4461,34 @@
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A109" s="2" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="D109" s="2">
-        <v>559</v>
+        <v>564</v>
       </c>
       <c r="E109" s="2">
-        <v>578</v>
+        <v>421</v>
       </c>
       <c r="F109" s="2">
-        <v>-19</v>
+        <v>143</v>
       </c>
       <c r="G109" s="2">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H109" s="2">
         <v>30</v>
       </c>
       <c r="I109" s="2">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="J109" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K109" s="2" t="s">
         <v>15</v>
@@ -4550,22 +4496,22 @@
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A110" s="2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D110" s="2">
-        <v>614</v>
+        <v>564</v>
       </c>
       <c r="E110" s="2">
-        <v>578</v>
+        <v>421</v>
       </c>
       <c r="F110" s="2">
-        <v>36</v>
+        <v>143</v>
       </c>
       <c r="G110" s="2">
         <v>40</v>
@@ -4577,7 +4523,7 @@
         <v>-10</v>
       </c>
       <c r="J110" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K110" s="2" t="s">
         <v>15</v>
@@ -4585,34 +4531,34 @@
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A111" s="2" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="D111" s="2">
-        <v>687</v>
+        <v>369</v>
       </c>
       <c r="E111" s="2">
-        <v>578</v>
+        <v>623</v>
       </c>
       <c r="F111" s="2">
-        <v>109</v>
+        <v>-254</v>
       </c>
       <c r="G111" s="2">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="H111" s="2">
         <v>30</v>
       </c>
       <c r="I111" s="2">
-        <v>-10</v>
+        <v>15</v>
       </c>
       <c r="J111" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K111" s="2" t="s">
         <v>15</v>
@@ -4620,34 +4566,34 @@
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A112" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="D112" s="2">
-        <v>559</v>
+        <v>465</v>
       </c>
       <c r="E112" s="2">
-        <v>578</v>
+        <v>623</v>
       </c>
       <c r="F112" s="2">
-        <v>-19</v>
+        <v>-158</v>
       </c>
       <c r="G112" s="2">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H112" s="2">
         <v>30</v>
       </c>
       <c r="I112" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J112" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K112" s="2" t="s">
         <v>15</v>
@@ -4655,34 +4601,34 @@
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A113" s="2" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D113" s="2">
-        <v>614</v>
+        <v>369</v>
       </c>
       <c r="E113" s="2">
-        <v>578</v>
+        <v>623</v>
       </c>
       <c r="F113" s="2">
-        <v>36</v>
+        <v>-254</v>
       </c>
       <c r="G113" s="2">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="H113" s="2">
         <v>30</v>
       </c>
       <c r="I113" s="2">
-        <v>-10</v>
+        <v>15</v>
       </c>
       <c r="J113" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K113" s="2" t="s">
         <v>15</v>
@@ -4690,34 +4636,34 @@
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A114" s="2" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="B114" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>30</v>
+        <v>71</v>
       </c>
       <c r="D114" s="2">
-        <v>614</v>
+        <v>369</v>
       </c>
       <c r="E114" s="2">
-        <v>539</v>
+        <v>623</v>
       </c>
       <c r="F114" s="2">
-        <v>75</v>
+        <v>-254</v>
       </c>
       <c r="G114" s="2">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="H114" s="2">
         <v>30</v>
       </c>
       <c r="I114" s="2">
-        <v>-10</v>
+        <v>15</v>
       </c>
       <c r="J114" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K114" s="2" t="s">
         <v>15</v>
@@ -4725,34 +4671,34 @@
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A115" s="2" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D115" s="2">
-        <v>420</v>
+        <v>369</v>
       </c>
       <c r="E115" s="2">
-        <v>421</v>
+        <v>623</v>
       </c>
       <c r="F115" s="2">
-        <v>-1</v>
+        <v>-254</v>
       </c>
       <c r="G115" s="2">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="H115" s="2">
         <v>30</v>
       </c>
       <c r="I115" s="2">
-        <v>-10</v>
+        <v>15</v>
       </c>
       <c r="J115" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K115" s="2" t="s">
         <v>15</v>
@@ -4760,34 +4706,34 @@
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A116" s="2" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="D116" s="2">
-        <v>550</v>
+        <v>369</v>
       </c>
       <c r="E116" s="2">
-        <v>539</v>
+        <v>623</v>
       </c>
       <c r="F116" s="2">
-        <v>11</v>
+        <v>-254</v>
       </c>
       <c r="G116" s="2">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="H116" s="2">
         <v>30</v>
       </c>
       <c r="I116" s="2">
-        <v>-10</v>
+        <v>15</v>
       </c>
       <c r="J116" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K116" s="2" t="s">
         <v>15</v>
@@ -4795,34 +4741,34 @@
     </row>
     <row r="117" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A117" s="2" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>30</v>
+        <v>71</v>
       </c>
       <c r="D117" s="2">
-        <v>614</v>
+        <v>369</v>
       </c>
       <c r="E117" s="2">
-        <v>539</v>
+        <v>623</v>
       </c>
       <c r="F117" s="2">
-        <v>75</v>
+        <v>-254</v>
       </c>
       <c r="G117" s="2">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="H117" s="2">
         <v>30</v>
       </c>
       <c r="I117" s="2">
-        <v>-10</v>
+        <v>15</v>
       </c>
       <c r="J117" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K117" s="2" t="s">
         <v>15</v>
@@ -4830,34 +4776,34 @@
     </row>
     <row r="118" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A118" s="2" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="D118" s="2">
-        <v>614</v>
+        <v>465</v>
       </c>
       <c r="E118" s="2">
-        <v>539</v>
+        <v>623</v>
       </c>
       <c r="F118" s="2">
-        <v>75</v>
+        <v>-158</v>
       </c>
       <c r="G118" s="2">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="H118" s="2">
         <v>30</v>
       </c>
       <c r="I118" s="2">
-        <v>-10</v>
+        <v>10</v>
       </c>
       <c r="J118" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K118" s="2" t="s">
         <v>15</v>
@@ -4865,34 +4811,34 @@
     </row>
     <row r="119" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A119" s="2" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D119" s="2">
-        <v>684</v>
+        <v>639</v>
       </c>
       <c r="E119" s="2">
-        <v>539</v>
+        <v>883</v>
       </c>
       <c r="F119" s="2">
-        <v>145</v>
+        <v>-244</v>
       </c>
       <c r="G119" s="2">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="H119" s="2">
         <v>30</v>
       </c>
       <c r="I119" s="2">
-        <v>-10</v>
+        <v>15</v>
       </c>
       <c r="J119" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K119" s="2" t="s">
         <v>15</v>
@@ -4900,34 +4846,34 @@
     </row>
     <row r="120" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A120" s="2" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="B120" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D120" s="2">
-        <v>684</v>
+        <v>639</v>
       </c>
       <c r="E120" s="2">
-        <v>578</v>
+        <v>883</v>
       </c>
       <c r="F120" s="2">
-        <v>106</v>
+        <v>-244</v>
       </c>
       <c r="G120" s="2">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="H120" s="2">
         <v>30</v>
       </c>
       <c r="I120" s="2">
-        <v>-10</v>
+        <v>15</v>
       </c>
       <c r="J120" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K120" s="2" t="s">
         <v>15</v>
@@ -4935,34 +4881,34 @@
     </row>
     <row r="121" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A121" s="2" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>30</v>
+        <v>71</v>
       </c>
       <c r="D121" s="2">
-        <v>614</v>
+        <v>639</v>
       </c>
       <c r="E121" s="2">
-        <v>578</v>
+        <v>883</v>
       </c>
       <c r="F121" s="2">
-        <v>36</v>
+        <v>-244</v>
       </c>
       <c r="G121" s="2">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="H121" s="2">
         <v>30</v>
       </c>
       <c r="I121" s="2">
-        <v>-10</v>
+        <v>15</v>
       </c>
       <c r="J121" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K121" s="2" t="s">
         <v>15</v>
@@ -4970,34 +4916,34 @@
     </row>
     <row r="122" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A122" s="2" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="D122" s="2">
-        <v>630</v>
+        <v>465</v>
       </c>
       <c r="E122" s="2">
-        <v>578</v>
+        <v>623</v>
       </c>
       <c r="F122" s="2">
-        <v>52</v>
+        <v>-158</v>
       </c>
       <c r="G122" s="2">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="H122" s="2">
         <v>30</v>
       </c>
       <c r="I122" s="2">
-        <v>-10</v>
+        <v>10</v>
       </c>
       <c r="J122" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K122" s="2" t="s">
         <v>15</v>
@@ -5005,34 +4951,34 @@
     </row>
     <row r="123" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A123" s="2" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="B123" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="D123" s="2">
-        <v>614</v>
+        <v>465</v>
       </c>
       <c r="E123" s="2">
-        <v>539</v>
+        <v>623</v>
       </c>
       <c r="F123" s="2">
-        <v>75</v>
+        <v>-158</v>
       </c>
       <c r="G123" s="2">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="H123" s="2">
         <v>30</v>
       </c>
       <c r="I123" s="2">
-        <v>-10</v>
+        <v>10</v>
       </c>
       <c r="J123" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K123" s="2" t="s">
         <v>15</v>
@@ -5040,34 +4986,34 @@
     </row>
     <row r="124" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A124" s="2" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="D124" s="2">
-        <v>550</v>
+        <v>465</v>
       </c>
       <c r="E124" s="2">
-        <v>578</v>
+        <v>623</v>
       </c>
       <c r="F124" s="2">
-        <v>-28</v>
+        <v>-158</v>
       </c>
       <c r="G124" s="2">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="H124" s="2">
         <v>30</v>
       </c>
       <c r="I124" s="2">
-        <v>-10</v>
+        <v>10</v>
       </c>
       <c r="J124" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K124" s="2" t="s">
         <v>15</v>
@@ -5075,22 +5021,22 @@
     </row>
     <row r="125" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A125" s="2" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C125" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D125" s="2">
-        <v>420</v>
+        <v>684</v>
       </c>
       <c r="E125" s="2">
-        <v>421</v>
+        <v>623</v>
       </c>
       <c r="F125" s="2">
-        <v>-1</v>
+        <v>61</v>
       </c>
       <c r="G125" s="2">
         <v>40</v>
@@ -5102,7 +5048,7 @@
         <v>-10</v>
       </c>
       <c r="J125" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K125" s="2" t="s">
         <v>15</v>
@@ -5110,22 +5056,22 @@
     </row>
     <row r="126" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A126" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C126" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="B126" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C126" s="2" t="s">
-        <v>30</v>
-      </c>
       <c r="D126" s="2">
-        <v>614</v>
+        <v>684</v>
       </c>
       <c r="E126" s="2">
-        <v>539</v>
+        <v>623</v>
       </c>
       <c r="F126" s="2">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="G126" s="2">
         <v>40</v>
@@ -5137,7 +5083,7 @@
         <v>-10</v>
       </c>
       <c r="J126" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K126" s="2" t="s">
         <v>15</v>
@@ -5145,34 +5091,34 @@
     </row>
     <row r="127" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A127" s="2" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="D127" s="2">
-        <v>550</v>
+        <v>465</v>
       </c>
       <c r="E127" s="2">
-        <v>421</v>
+        <v>623</v>
       </c>
       <c r="F127" s="2">
-        <v>129</v>
+        <v>-158</v>
       </c>
       <c r="G127" s="2">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="H127" s="2">
         <v>30</v>
       </c>
       <c r="I127" s="2">
-        <v>-10</v>
+        <v>10</v>
       </c>
       <c r="J127" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K127" s="2" t="s">
         <v>15</v>
@@ -5180,1436 +5126,36 @@
     </row>
     <row r="128" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A128" s="2" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="D128" s="2">
-        <v>614</v>
+        <v>465</v>
       </c>
       <c r="E128" s="2">
-        <v>539</v>
+        <v>623</v>
       </c>
       <c r="F128" s="2">
-        <v>75</v>
+        <v>-158</v>
       </c>
       <c r="G128" s="2">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="H128" s="2">
         <v>30</v>
       </c>
       <c r="I128" s="2">
-        <v>-10</v>
+        <v>10</v>
       </c>
       <c r="J128" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K128" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A129" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B129" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C129" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D129" s="2">
-        <v>614</v>
-      </c>
-      <c r="E129" s="2">
-        <v>578</v>
-      </c>
-      <c r="F129" s="2">
-        <v>36</v>
-      </c>
-      <c r="G129" s="2">
-        <v>40</v>
-      </c>
-      <c r="H129" s="2">
-        <v>30</v>
-      </c>
-      <c r="I129" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J129" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="K129" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A130" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B130" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C130" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D130" s="2">
-        <v>693</v>
-      </c>
-      <c r="E130" s="2">
-        <v>578</v>
-      </c>
-      <c r="F130" s="2">
-        <v>115</v>
-      </c>
-      <c r="G130" s="2">
-        <v>40</v>
-      </c>
-      <c r="H130" s="2">
-        <v>30</v>
-      </c>
-      <c r="I130" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J130" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="K130" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A131" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="B131" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C131" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D131" s="2">
-        <v>614</v>
-      </c>
-      <c r="E131" s="2">
-        <v>539</v>
-      </c>
-      <c r="F131" s="2">
-        <v>75</v>
-      </c>
-      <c r="G131" s="2">
-        <v>40</v>
-      </c>
-      <c r="H131" s="2">
-        <v>30</v>
-      </c>
-      <c r="I131" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J131" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="K131" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A132" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="B132" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C132" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D132" s="2">
-        <v>614</v>
-      </c>
-      <c r="E132" s="2">
-        <v>539</v>
-      </c>
-      <c r="F132" s="2">
-        <v>75</v>
-      </c>
-      <c r="G132" s="2">
-        <v>40</v>
-      </c>
-      <c r="H132" s="2">
-        <v>30</v>
-      </c>
-      <c r="I132" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J132" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="K132" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="133" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A133" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="B133" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C133" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D133" s="2">
-        <v>614</v>
-      </c>
-      <c r="E133" s="2">
-        <v>623</v>
-      </c>
-      <c r="F133" s="2">
-        <v>-9</v>
-      </c>
-      <c r="G133" s="2">
-        <v>40</v>
-      </c>
-      <c r="H133" s="2">
-        <v>30</v>
-      </c>
-      <c r="I133" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J133" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="K133" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="134" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A134" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="B134" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C134" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D134" s="2">
-        <v>693</v>
-      </c>
-      <c r="E134" s="2">
-        <v>623</v>
-      </c>
-      <c r="F134" s="2">
-        <v>70</v>
-      </c>
-      <c r="G134" s="2">
-        <v>40</v>
-      </c>
-      <c r="H134" s="2">
-        <v>30</v>
-      </c>
-      <c r="I134" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J134" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="K134" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A135" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B135" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C135" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D135" s="2">
-        <v>614</v>
-      </c>
-      <c r="E135" s="2">
-        <v>623</v>
-      </c>
-      <c r="F135" s="2">
-        <v>-9</v>
-      </c>
-      <c r="G135" s="2">
-        <v>40</v>
-      </c>
-      <c r="H135" s="2">
-        <v>30</v>
-      </c>
-      <c r="I135" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J135" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="K135" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="136" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A136" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B136" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C136" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="D136" s="2">
-        <v>614</v>
-      </c>
-      <c r="E136" s="2">
-        <v>623</v>
-      </c>
-      <c r="F136" s="2">
-        <v>-9</v>
-      </c>
-      <c r="G136" s="2">
-        <v>40</v>
-      </c>
-      <c r="H136" s="2">
-        <v>30</v>
-      </c>
-      <c r="I136" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J136" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="K136" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A137" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B137" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C137" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D137" s="2">
-        <v>693</v>
-      </c>
-      <c r="E137" s="2">
-        <v>623</v>
-      </c>
-      <c r="F137" s="2">
-        <v>70</v>
-      </c>
-      <c r="G137" s="2">
-        <v>40</v>
-      </c>
-      <c r="H137" s="2">
-        <v>30</v>
-      </c>
-      <c r="I137" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J137" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="K137" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A138" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="B138" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C138" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D138" s="2">
-        <v>914</v>
-      </c>
-      <c r="E138" s="2">
-        <v>883</v>
-      </c>
-      <c r="F138" s="2">
-        <v>31</v>
-      </c>
-      <c r="G138" s="2">
-        <v>40</v>
-      </c>
-      <c r="H138" s="2">
-        <v>30</v>
-      </c>
-      <c r="I138" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J138" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="K138" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="139" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A139" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="B139" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C139" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="D139" s="2">
-        <v>914</v>
-      </c>
-      <c r="E139" s="2">
-        <v>883</v>
-      </c>
-      <c r="F139" s="2">
-        <v>31</v>
-      </c>
-      <c r="G139" s="2">
-        <v>40</v>
-      </c>
-      <c r="H139" s="2">
-        <v>30</v>
-      </c>
-      <c r="I139" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J139" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="K139" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="140" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A140" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="B140" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C140" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D140" s="2">
-        <v>834</v>
-      </c>
-      <c r="E140" s="2">
-        <v>883</v>
-      </c>
-      <c r="F140" s="2">
-        <v>-49</v>
-      </c>
-      <c r="G140" s="2">
-        <v>40</v>
-      </c>
-      <c r="H140" s="2">
-        <v>30</v>
-      </c>
-      <c r="I140" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J140" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="K140" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="141" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A141" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="B141" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C141" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D141" s="2">
-        <v>639</v>
-      </c>
-      <c r="E141" s="2">
-        <v>883</v>
-      </c>
-      <c r="F141" s="2">
-        <v>-244</v>
-      </c>
-      <c r="G141" s="2">
-        <v>15</v>
-      </c>
-      <c r="H141" s="2">
-        <v>30</v>
-      </c>
-      <c r="I141" s="2">
-        <v>15</v>
-      </c>
-      <c r="J141" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="K141" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="142" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A142" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="B142" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C142" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="D142" s="2">
-        <v>639</v>
-      </c>
-      <c r="E142" s="2">
-        <v>883</v>
-      </c>
-      <c r="F142" s="2">
-        <v>-244</v>
-      </c>
-      <c r="G142" s="2">
-        <v>15</v>
-      </c>
-      <c r="H142" s="2">
-        <v>30</v>
-      </c>
-      <c r="I142" s="2">
-        <v>15</v>
-      </c>
-      <c r="J142" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="K142" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="143" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A143" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="B143" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C143" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D143" s="2">
-        <v>644</v>
-      </c>
-      <c r="E143" s="2">
-        <v>623</v>
-      </c>
-      <c r="F143" s="2">
-        <v>21</v>
-      </c>
-      <c r="G143" s="2">
-        <v>40</v>
-      </c>
-      <c r="H143" s="2">
-        <v>30</v>
-      </c>
-      <c r="I143" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J143" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="K143" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="144" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A144" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B144" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C144" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D144" s="2">
-        <v>614</v>
-      </c>
-      <c r="E144" s="2">
-        <v>623</v>
-      </c>
-      <c r="F144" s="2">
-        <v>-9</v>
-      </c>
-      <c r="G144" s="2">
-        <v>40</v>
-      </c>
-      <c r="H144" s="2">
-        <v>30</v>
-      </c>
-      <c r="I144" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J144" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="K144" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="145" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A145" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="B145" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C145" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D145" s="2">
-        <v>466</v>
-      </c>
-      <c r="E145" s="2">
-        <v>623</v>
-      </c>
-      <c r="F145" s="2">
-        <v>-157</v>
-      </c>
-      <c r="G145" s="2">
-        <v>20</v>
-      </c>
-      <c r="H145" s="2">
-        <v>30</v>
-      </c>
-      <c r="I145" s="2">
-        <v>10</v>
-      </c>
-      <c r="J145" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="K145" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="146" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A146" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="B146" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C146" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D146" s="2">
-        <v>614</v>
-      </c>
-      <c r="E146" s="2">
-        <v>623</v>
-      </c>
-      <c r="F146" s="2">
-        <v>-9</v>
-      </c>
-      <c r="G146" s="2">
-        <v>40</v>
-      </c>
-      <c r="H146" s="2">
-        <v>30</v>
-      </c>
-      <c r="I146" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J146" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="K146" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="147" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A147" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="B147" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C147" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="D147" s="2">
-        <v>614</v>
-      </c>
-      <c r="E147" s="2">
-        <v>623</v>
-      </c>
-      <c r="F147" s="2">
-        <v>-9</v>
-      </c>
-      <c r="G147" s="2">
-        <v>40</v>
-      </c>
-      <c r="H147" s="2">
-        <v>30</v>
-      </c>
-      <c r="I147" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J147" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="K147" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="148" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A148" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="B148" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C148" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D148" s="2">
-        <v>614</v>
-      </c>
-      <c r="E148" s="2">
-        <v>623</v>
-      </c>
-      <c r="F148" s="2">
-        <v>-9</v>
-      </c>
-      <c r="G148" s="2">
-        <v>40</v>
-      </c>
-      <c r="H148" s="2">
-        <v>30</v>
-      </c>
-      <c r="I148" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J148" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="K148" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="149" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A149" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="B149" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C149" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="D149" s="2">
-        <v>614</v>
-      </c>
-      <c r="E149" s="2">
-        <v>623</v>
-      </c>
-      <c r="F149" s="2">
-        <v>-9</v>
-      </c>
-      <c r="G149" s="2">
-        <v>40</v>
-      </c>
-      <c r="H149" s="2">
-        <v>30</v>
-      </c>
-      <c r="I149" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J149" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="K149" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="150" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A150" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="B150" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C150" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="D150" s="2">
-        <v>644</v>
-      </c>
-      <c r="E150" s="2">
-        <v>623</v>
-      </c>
-      <c r="F150" s="2">
-        <v>21</v>
-      </c>
-      <c r="G150" s="2">
-        <v>40</v>
-      </c>
-      <c r="H150" s="2">
-        <v>30</v>
-      </c>
-      <c r="I150" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J150" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="K150" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="151" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A151" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="B151" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C151" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D151" s="2">
-        <v>614</v>
-      </c>
-      <c r="E151" s="2">
-        <v>623</v>
-      </c>
-      <c r="F151" s="2">
-        <v>-9</v>
-      </c>
-      <c r="G151" s="2">
-        <v>40</v>
-      </c>
-      <c r="H151" s="2">
-        <v>30</v>
-      </c>
-      <c r="I151" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J151" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="K151" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="152" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A152" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B152" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C152" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D152" s="2">
-        <v>466</v>
-      </c>
-      <c r="E152" s="2">
-        <v>623</v>
-      </c>
-      <c r="F152" s="2">
-        <v>-157</v>
-      </c>
-      <c r="G152" s="2">
-        <v>20</v>
-      </c>
-      <c r="H152" s="2">
-        <v>30</v>
-      </c>
-      <c r="I152" s="2">
-        <v>10</v>
-      </c>
-      <c r="J152" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="K152" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="153" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A153" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="B153" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C153" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D153" s="2">
-        <v>614</v>
-      </c>
-      <c r="E153" s="2">
-        <v>623</v>
-      </c>
-      <c r="F153" s="2">
-        <v>-9</v>
-      </c>
-      <c r="G153" s="2">
-        <v>40</v>
-      </c>
-      <c r="H153" s="2">
-        <v>30</v>
-      </c>
-      <c r="I153" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J153" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="K153" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="154" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A154" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="B154" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C154" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="D154" s="2">
-        <v>614</v>
-      </c>
-      <c r="E154" s="2">
-        <v>623</v>
-      </c>
-      <c r="F154" s="2">
-        <v>-9</v>
-      </c>
-      <c r="G154" s="2">
-        <v>40</v>
-      </c>
-      <c r="H154" s="2">
-        <v>30</v>
-      </c>
-      <c r="I154" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J154" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="K154" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="155" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A155" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="B155" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C155" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D155" s="2">
-        <v>684</v>
-      </c>
-      <c r="E155" s="2">
-        <v>623</v>
-      </c>
-      <c r="F155" s="2">
-        <v>61</v>
-      </c>
-      <c r="G155" s="2">
-        <v>40</v>
-      </c>
-      <c r="H155" s="2">
-        <v>30</v>
-      </c>
-      <c r="I155" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J155" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="K155" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="156" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A156" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="B156" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C156" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D156" s="2">
-        <v>466</v>
-      </c>
-      <c r="E156" s="2">
-        <v>623</v>
-      </c>
-      <c r="F156" s="2">
-        <v>-157</v>
-      </c>
-      <c r="G156" s="2">
-        <v>20</v>
-      </c>
-      <c r="H156" s="2">
-        <v>30</v>
-      </c>
-      <c r="I156" s="2">
-        <v>10</v>
-      </c>
-      <c r="J156" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="K156" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="157" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A157" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="B157" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C157" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D157" s="2">
-        <v>684</v>
-      </c>
-      <c r="E157" s="2">
-        <v>623</v>
-      </c>
-      <c r="F157" s="2">
-        <v>61</v>
-      </c>
-      <c r="G157" s="2">
-        <v>40</v>
-      </c>
-      <c r="H157" s="2">
-        <v>30</v>
-      </c>
-      <c r="I157" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J157" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="K157" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="158" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A158" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="B158" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C158" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D158" s="2">
-        <v>614</v>
-      </c>
-      <c r="E158" s="2">
-        <v>623</v>
-      </c>
-      <c r="F158" s="2">
-        <v>-9</v>
-      </c>
-      <c r="G158" s="2">
-        <v>40</v>
-      </c>
-      <c r="H158" s="2">
-        <v>30</v>
-      </c>
-      <c r="I158" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J158" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="K158" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="159" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A159" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="B159" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C159" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="D159" s="2">
-        <v>614</v>
-      </c>
-      <c r="E159" s="2">
-        <v>623</v>
-      </c>
-      <c r="F159" s="2">
-        <v>-9</v>
-      </c>
-      <c r="G159" s="2">
-        <v>40</v>
-      </c>
-      <c r="H159" s="2">
-        <v>30</v>
-      </c>
-      <c r="I159" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J159" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="K159" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="160" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A160" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="B160" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C160" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D160" s="2">
-        <v>644</v>
-      </c>
-      <c r="E160" s="2">
-        <v>623</v>
-      </c>
-      <c r="F160" s="2">
-        <v>21</v>
-      </c>
-      <c r="G160" s="2">
-        <v>40</v>
-      </c>
-      <c r="H160" s="2">
-        <v>30</v>
-      </c>
-      <c r="I160" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J160" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="K160" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="161" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A161" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="B161" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C161" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="D161" s="2">
-        <v>644</v>
-      </c>
-      <c r="E161" s="2">
-        <v>623</v>
-      </c>
-      <c r="F161" s="2">
-        <v>21</v>
-      </c>
-      <c r="G161" s="2">
-        <v>40</v>
-      </c>
-      <c r="H161" s="2">
-        <v>30</v>
-      </c>
-      <c r="I161" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J161" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="K161" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="162" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A162" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="B162" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C162" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D162" s="2">
-        <v>466</v>
-      </c>
-      <c r="E162" s="2">
-        <v>623</v>
-      </c>
-      <c r="F162" s="2">
-        <v>-157</v>
-      </c>
-      <c r="G162" s="2">
-        <v>20</v>
-      </c>
-      <c r="H162" s="2">
-        <v>30</v>
-      </c>
-      <c r="I162" s="2">
-        <v>10</v>
-      </c>
-      <c r="J162" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="K162" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="163" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A163" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="B163" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C163" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D163" s="2">
-        <v>614</v>
-      </c>
-      <c r="E163" s="2">
-        <v>623</v>
-      </c>
-      <c r="F163" s="2">
-        <v>-9</v>
-      </c>
-      <c r="G163" s="2">
-        <v>40</v>
-      </c>
-      <c r="H163" s="2">
-        <v>30</v>
-      </c>
-      <c r="I163" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J163" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="K163" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="164" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A164" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="B164" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C164" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="D164" s="2">
-        <v>644</v>
-      </c>
-      <c r="E164" s="2">
-        <v>623</v>
-      </c>
-      <c r="F164" s="2">
-        <v>21</v>
-      </c>
-      <c r="G164" s="2">
-        <v>40</v>
-      </c>
-      <c r="H164" s="2">
-        <v>30</v>
-      </c>
-      <c r="I164" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J164" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="K164" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="165" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A165" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="B165" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C165" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D165" s="2">
-        <v>466</v>
-      </c>
-      <c r="E165" s="2">
-        <v>623</v>
-      </c>
-      <c r="F165" s="2">
-        <v>-157</v>
-      </c>
-      <c r="G165" s="2">
-        <v>20</v>
-      </c>
-      <c r="H165" s="2">
-        <v>30</v>
-      </c>
-      <c r="I165" s="2">
-        <v>10</v>
-      </c>
-      <c r="J165" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="K165" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="166" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A166" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="B166" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C166" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="D166" s="2">
-        <v>614</v>
-      </c>
-      <c r="E166" s="2">
-        <v>623</v>
-      </c>
-      <c r="F166" s="2">
-        <v>-9</v>
-      </c>
-      <c r="G166" s="2">
-        <v>40</v>
-      </c>
-      <c r="H166" s="2">
-        <v>30</v>
-      </c>
-      <c r="I166" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J166" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="K166" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="167" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A167" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="B167" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C167" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D167" s="2">
-        <v>614</v>
-      </c>
-      <c r="E167" s="2">
-        <v>623</v>
-      </c>
-      <c r="F167" s="2">
-        <v>-9</v>
-      </c>
-      <c r="G167" s="2">
-        <v>40</v>
-      </c>
-      <c r="H167" s="2">
-        <v>30</v>
-      </c>
-      <c r="I167" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J167" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="K167" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="168" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A168" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="B168" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C168" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="D168" s="2">
-        <v>614</v>
-      </c>
-      <c r="E168" s="2">
-        <v>623</v>
-      </c>
-      <c r="F168" s="2">
-        <v>-9</v>
-      </c>
-      <c r="G168" s="2">
-        <v>40</v>
-      </c>
-      <c r="H168" s="2">
-        <v>30</v>
-      </c>
-      <c r="I168" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J168" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="K168" s="2" t="s">
         <v>15</v>
       </c>
     </row>
